--- a/examples/sample_output/report.xlsx
+++ b/examples/sample_output/report.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>AR5('06 IPCC 지침 기준 — 공표문 각주 명시)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2023년 국가 전력배출계수(소비단), 기후에너지환경부·온실가스종합정보센터, 국가 온실가스 통계관리위원회 확정, 2025.12 공표</t>
+          <t>「2025년 승인 국가 온실가스 배출·흡수계수」 전력배출계수, '23년 소비단 CO2-eq — 온실가스종합정보센터(기획총괄팀), 2025-12-18 공표</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/examples/sample_output/report.xlsx
+++ b/examples/sample_output/report.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +588,26 @@
           <t>배출량(kg)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>수기교정</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>교정자</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>교정일시</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>교정근거</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -630,6 +650,10 @@
       <c r="J2" t="n">
         <v>10.607</v>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -669,6 +693,10 @@
       <c r="J3" t="n">
         <v>128.85</v>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,6 +736,10 @@
       <c r="J4" t="n">
         <v>208.65</v>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,6 +782,10 @@
       <c r="J5" t="n">
         <v>220.176</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -792,6 +828,10 @@
       <c r="J6" t="n">
         <v>429.502</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -834,6 +874,10 @@
       <c r="J7" t="n">
         <v>1809.5</v>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -876,6 +920,10 @@
       <c r="J8" t="n">
         <v>1512.84</v>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -918,6 +966,10 @@
       <c r="J9" t="n">
         <v>4800</v>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -960,6 +1012,10 @@
       <c r="J10" t="n">
         <v>5000</v>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1002,6 +1058,10 @@
       <c r="J11" t="n">
         <v>104325</v>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1044,6 +1104,10 @@
       <c r="J12" t="n">
         <v>125190</v>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1086,6 +1150,10 @@
       <c r="J13" t="n">
         <v>26.652</v>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1128,6 +1196,10 @@
       <c r="J14" t="n">
         <v>8346</v>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1170,6 +1242,10 @@
       <c r="J15" t="n">
         <v>25038</v>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1212,6 +1288,10 @@
       <c r="J16" t="n">
         <v>4364</v>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1254,6 +1334,10 @@
       <c r="J17" t="n">
         <v>50000</v>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1296,6 +1380,10 @@
       <c r="J18" t="n">
         <v>120000</v>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1338,6 +1426,10 @@
       <c r="J19" t="n">
         <v>1350</v>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1380,6 +1472,10 @@
       <c r="J20" t="n">
         <v>4500</v>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1422,6 +1518,10 @@
       <c r="J21" t="n">
         <v>1462.8</v>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1464,6 +1564,10 @@
       <c r="J22" t="n">
         <v>222.32</v>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1506,6 +1610,10 @@
       <c r="J23" t="n">
         <v>1040.668</v>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1548,6 +1656,10 @@
       <c r="J24" t="n">
         <v>9.616</v>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1590,6 +1702,10 @@
       <c r="J25" t="n">
         <v>3338.4</v>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1632,6 +1748,10 @@
       <c r="J26" t="n">
         <v>1251.9</v>
       </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1674,6 +1794,10 @@
       <c r="J27" t="n">
         <v>585.12</v>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1716,6 +1840,10 @@
       <c r="J28" t="n">
         <v>806</v>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1758,6 +1886,10 @@
       <c r="J29" t="n">
         <v>30.551</v>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1800,6 +1932,10 @@
       <c r="J30" t="n">
         <v>22.95</v>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1842,6 +1978,10 @@
       <c r="J31" t="n">
         <v>9.15</v>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/sample_output/report.xlsx
+++ b/examples/sample_output/report.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,25 +585,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>계수출처</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>배출량(kg)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>수기교정</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>교정자</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>교정일시</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>교정근거</t>
         </is>
@@ -647,13 +652,14 @@
           <t>kgCO2eq/passenger-km</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>10.607</v>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -690,13 +696,14 @@
           <t>kgCO2/L</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>128.85</v>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -733,13 +740,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>208.65</v>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -779,13 +787,14 @@
           <t>kgCO2eq/passenger-km</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>220.176</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -825,13 +834,14 @@
           <t>kgCO2eq/passenger-km</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>429.502</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -871,13 +881,14 @@
           <t>kgCO2eq/km</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>1809.5</v>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -917,13 +928,14 @@
           <t>kgCO2eq/km</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>1512.84</v>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -963,13 +975,18 @@
           <t>kgCO2eq/KRW</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>한국은행 환경산업연관표(2006) 도소매 부문 — 예시값(실제 산정 시 소관 계수로 교체)</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>4800</v>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1009,13 +1026,18 @@
           <t>kgCO2eq/KRW</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>한국은행 환경산업연관표(2006) 사업서비스 부문 — 예시값</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>5000</v>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1055,13 +1077,18 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>고객 가공공정 전력 원단위 추정×국가전력계수</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>104325</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1101,13 +1128,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
         <v>125190</v>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1147,13 +1175,14 @@
           <t>kgCO2eq/tonne</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
         <v>26.652</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1193,13 +1222,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
         <v>8346</v>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1239,13 +1269,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
         <v>25038</v>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1285,13 +1316,14 @@
           <t>kgCO2/Nm3</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
         <v>4364</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1331,13 +1363,18 @@
           <t>귀속계수(잔액/기업가치)</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PCAF 귀속공식 · 피투자 배출량 출처: 피투자사 2025 지속가능경영보고서 공시치(Scope1+2)</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>50000</v>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1377,13 +1414,18 @@
           <t>귀속계수(잔액/기업가치)</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>PCAF 귀속공식 · 피투자 배출량 출처: 피투자사 제출 명세서 검증본(2025)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>120000</v>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1423,13 +1465,18 @@
           <t>kgCO2eq/KRW</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>예시값(실제 산정 시 소관 산업계수로 교체)</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>1350</v>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1469,13 +1516,18 @@
           <t>kgCO2eq/KRW</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>예시값(한국은행 환경산업연관표 전자부문 준용 권장)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>4500</v>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1515,13 +1567,14 @@
           <t>kgCO2eq/tonne-km</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
         <v>1462.8</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1561,13 +1614,14 @@
           <t>kgCO2eq/tonne-km</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
         <v>222.32</v>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1607,13 +1661,14 @@
           <t>kgCO2eq/tonne</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
         <v>1040.668</v>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1653,13 +1708,14 @@
           <t>kgCO2eq/tonne</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
         <v>9.616</v>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1699,13 +1755,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
         <v>3338.4</v>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1745,13 +1802,18 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>국가 전력배출계수 2023 준용(사용자 확인)</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>1251.9</v>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1791,13 +1853,14 @@
           <t>kgCO2eq/tonne-km</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
         <v>585.12</v>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1837,13 +1900,14 @@
           <t>kgCO2eq/tonne-km</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
         <v>806</v>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1883,13 +1947,14 @@
           <t>kgCO2eq/L</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
         <v>30.551</v>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1929,13 +1994,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
         <v>22.95</v>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1975,13 +2041,14 @@
           <t>kgCO2eq/kWh</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
         <v>9.15</v>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2346,7 +2413,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>행별 factor_source 참조(건별 명세)</t>
+          <t>사용자 입력 계수 — 행별 출처는 §4 건별 명세의 '계수 출처' 열</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2512,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>행별 factor_source 참조(건별 명세)</t>
+          <t>사용자 입력 계수 — 행별 출처는 §4 건별 명세의 '계수 출처' 열</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output/report.xlsx
+++ b/examples/sample_output/report.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output/report.xlsx
+++ b/examples/sample_output/report.xlsx
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>465701.752</v>
+        <v>465688.625</v>
       </c>
       <c r="C8" t="n">
-        <v>465.702</v>
+        <v>465.689</v>
       </c>
     </row>
     <row r="9">
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>466039.252</v>
+        <v>466026.125</v>
       </c>
       <c r="C9" t="n">
-        <v>466.039</v>
+        <v>466.026</v>
       </c>
     </row>
     <row r="10"/>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.0278</v>
+        <v>0.01549</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>220.176</v>
+        <v>122.681</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.10846</v>
+        <v>0.10151</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>429.502</v>
+        <v>401.98</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.1645</v>
+        <v>0.16152</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>1809.5</v>
+        <v>1776.72</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.12607</v>
+        <v>0.12961</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>1512.84</v>
+        <v>1555.32</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.88386</v>
+        <v>9.006869999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>26.652</v>
+        <v>27.021</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.09752</v>
+        <v>0.10356</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>1462.8</v>
+        <v>1553.4</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.02779</v>
+        <v>0.02583</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>222.32</v>
+        <v>206.64</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>520.3342</v>
+        <v>520.58023</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>1040.668</v>
+        <v>1041.16</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.41061</v>
+        <v>4.65358</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>9.616</v>
+        <v>6.98</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.09752</v>
+        <v>0.10356</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>585.12</v>
+        <v>621.36</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.0459</v>
+        <v>0.03682</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>22.95</v>
+        <v>18.41</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.0183</v>
+        <v>0.01299</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>9.15</v>
+        <v>6.495</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0278</v>
+        <v>0.01549</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, London Underground (한국 지하철 공식 인·km 계수 부재로 대용)</t>
+          <t>DEFRA/DESNZ 2026, London Underground (한국 지하철 공식 인·km 계수 부재로 대용)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.10846</v>
+        <v>0.10151</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Average local bus</t>
+          <t>DEFRA/DESNZ 2026, Average local bus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1645</v>
+        <v>0.16152</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Average car/Petrol</t>
+          <t>DEFRA/DESNZ 2026, Average car/Petrol</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.12607</v>
+        <v>0.12961</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Average car/Hybrid</t>
+          <t>DEFRA/DESNZ 2026, Average car/Hybrid</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.88386</v>
+        <v>9.006869999999999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Waste disposal (Plastics: average, Landfill)</t>
+          <t>DEFRA/DESNZ 2026, Waste disposal (Plastics: average, Landfill)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09752</v>
+        <v>0.10356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Freighting goods (All HGVs, average laden, diesel)</t>
+          <t>DEFRA/DESNZ 2026, Freighting goods (Average non-refrigerated HGVs, average laden, diesel)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02779</v>
+        <v>0.02583</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Freighting goods (Rail, freight train)</t>
+          <t>DEFRA/DESNZ 2026, Freighting goods (Rail, freight train)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>520.3342</v>
+        <v>520.58023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Waste disposal (Commercial and industrial waste, Landfill)</t>
+          <t>DEFRA/DESNZ 2026, Waste disposal (Commercial and industrial waste, Landfill)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.41061</v>
+        <v>4.65358</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Waste disposal (recycling, closed/open-loop process stage)</t>
+          <t>DEFRA/DESNZ 2026, Waste disposal (Commercial and industrial waste, Closed-loop recycling)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Freighting goods (Cargo ship, container, average)</t>
+          <t>DEFRA/DESNZ 2026, Freighting goods (Cargo ship, container, average)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, WTT- fuels (diesel average)</t>
+          <t>DEFRA/DESNZ 2026, WTT- fuels (diesel average)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0459</v>
+        <v>0.03682</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2959,12 +2959,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, WTT- UK electricity (generation) — 한국 값 부재로 UK 프록시</t>
+          <t>DEFRA/DESNZ 2026, WTT- UK electricity (generation) — 한국 값 부재로 UK 프록시</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0183</v>
+        <v>0.01299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DEFRA/DESNZ 2024, Transmission and distribution — 한국 값 부재로 UK 프록시</t>
+          <t>DEFRA/DESNZ 2026, Transmission and distribution — 한국 값 부재로 UK 프록시</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2024</t>
+          <t>https://www.gov.uk/government/publications/greenhouse-gas-reporting-conversion-factors-2026</t>
         </is>
       </c>
     </row>

--- a/examples/sample_output/report.xlsx
+++ b/examples/sample_output/report.xlsx
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,11 @@
           <t>교정근거</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>거리산정근거</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -846,6 +851,11 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>서울→내장 역좌표 (37.5547,126.9707) / 부산→내장 역좌표 (35.1151,129.0403) / 대권 328.5km ×1.2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -890,6 +900,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -934,6 +945,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -981,6 +993,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1028,6 +1041,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1075,6 +1089,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1122,6 +1137,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1189,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1224,6 +1241,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1275,6 +1293,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1322,6 +1341,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1369,6 +1389,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1416,6 +1437,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1463,6 +1485,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1510,6 +1533,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1561,6 +1585,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1612,6 +1637,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1663,6 +1689,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1714,6 +1741,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1761,6 +1789,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1808,6 +1837,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1855,6 +1885,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1902,6 +1933,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1949,6 +1981,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2000,6 +2033,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2047,6 +2081,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2094,6 +2129,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2141,6 +2177,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2188,6 +2225,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2235,6 +2273,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
